--- a/Config/Datas/EncounterDatas/Encounters.xlsx
+++ b/Config/Datas/EncounterDatas/Encounters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\EncounterDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4234EE25-2321-4E10-9261-BDC33717FFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8FD9A2-3328-4837-AD7C-F79AC35E8346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,11 +209,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -531,24 +531,24 @@
       <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
       <c r="W1" s="1"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
@@ -570,24 +570,24 @@
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
       <c r="W2" s="1"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -628,20 +628,20 @@
       <c r="H4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
       <c r="S4" s="7" t="s">
         <v>14</v>
       </c>
@@ -656,31 +656,31 @@
       <c r="I5" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
       <c r="O5" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
       <c r="S5" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
       <c r="W5" s="4"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
